--- a/src/Excelsior.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/Excelsior.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -22,8 +22,8 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
-      <color rgb="0563C1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,8 +125,8 @@
           </r>
           <r>
             <rPr>
+              <color rgb="FF0563C1"/>
               <u/>
-              <color rgb="0563C1"/>
             </rPr>
             <t xml:space="preserve">https://google.com</t>
           </r>
@@ -142,8 +142,8 @@
           </r>
           <r>
             <rPr>
+              <color rgb="FF0563C1"/>
               <u/>
-              <color rgb="0563C1"/>
             </rPr>
             <t xml:space="preserve">https://github.com</t>
           </r>
@@ -160,8 +160,8 @@
           </r>
           <r>
             <rPr>
+              <color rgb="FF0563C1"/>
               <u/>
-              <color rgb="0563C1"/>
             </rPr>
             <t xml:space="preserve">https://google.com</t>
           </r>

--- a/src/Excelsior.Tests/LinkTests.UrlOnly.verified.xlsx
+++ b/src/Excelsior.Tests/LinkTests.UrlOnly.verified.xlsx
@@ -179,7 +179,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Link"/>
